--- a/data/P1/P1T1_BQ1.xlsx
+++ b/data/P1/P1T1_BQ1.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/單詞複習網素材/data/P1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7286A7A5-7E67-534D-87FA-F472E533C11A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{963CE813-FFBA-C94C-9F85-D516429E6181}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="460" windowWidth="24820" windowHeight="15020" xr2:uid="{90F29878-E095-0247-8CA8-B281629F062F}"/>
+    <workbookView xWindow="28460" yWindow="3780" windowWidth="24820" windowHeight="15020" activeTab="1" xr2:uid="{90F29878-E095-0247-8CA8-B281629F062F}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
+    <sheet name="工作表2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
   <si>
     <t>word</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -157,13 +158,49 @@
   </si>
   <si>
     <t>同校同學</t>
+  </si>
+  <si>
+    <t>sentence</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chinese</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>We live in families.</t>
+  </si>
+  <si>
+    <t>Some families are big. Some families are small.</t>
+  </si>
+  <si>
+    <t>Families help each other.</t>
+  </si>
+  <si>
+    <t>Friends share things and play together.</t>
+  </si>
+  <si>
+    <t>我們生活在家庭裡。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>有些家庭很大，有些家庭很小。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>家人會互相幫助。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>朋友會分享東西，並且一起玩。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -199,6 +236,12 @@
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -222,7 +265,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -233,6 +276,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -822,4 +868,59 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A155953-E077-1948-964D-399DF6EBA5E0}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="48.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="16">
+      <c r="A2" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="16">
+      <c r="A3" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="16">
+      <c r="A4" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="16">
+      <c r="A5" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/P1/P1T1_BQ1.xlsx
+++ b/data/P1/P1T1_BQ1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/單詞複習網素材/data/P1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{963CE813-FFBA-C94C-9F85-D516429E6181}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D8F8F85-0B5B-2C48-A13B-0CE3BDB372CA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28460" yWindow="3780" windowWidth="24820" windowHeight="15020" activeTab="1" xr2:uid="{90F29878-E095-0247-8CA8-B281629F062F}"/>
+    <workbookView xWindow="28460" yWindow="3780" windowWidth="30940" windowHeight="15020" xr2:uid="{90F29878-E095-0247-8CA8-B281629F062F}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="93">
   <si>
     <t>word</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -194,13 +194,133 @@
   <si>
     <t>朋友會分享東西，並且一起玩。</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>phonetics</t>
+  </si>
+  <si>
+    <t>syllable</t>
+  </si>
+  <si>
+    <t>/ˈfæməli/</t>
+  </si>
+  <si>
+    <t>fam-i-ly</t>
+  </si>
+  <si>
+    <t>/ˈɡrændpeərənts/</t>
+  </si>
+  <si>
+    <t>grand-par-ents</t>
+  </si>
+  <si>
+    <t>/ˈɡrænfɑːðə(r)/</t>
+  </si>
+  <si>
+    <t>grand-fa-ther</t>
+  </si>
+  <si>
+    <t>/ˈɡrænmʌðə(r)/</t>
+  </si>
+  <si>
+    <t>grand-moth-er</t>
+  </si>
+  <si>
+    <t>/ˈpeərənts/</t>
+  </si>
+  <si>
+    <t>par-ents</t>
+  </si>
+  <si>
+    <t>/ˈfɑːðə(r)/</t>
+  </si>
+  <si>
+    <t>fa-ther</t>
+  </si>
+  <si>
+    <t>/ˈmʌðə(r)/</t>
+  </si>
+  <si>
+    <t>moth-er</t>
+  </si>
+  <si>
+    <t>/ˈsɪblɪŋz/</t>
+  </si>
+  <si>
+    <t>sib-lings</t>
+  </si>
+  <si>
+    <t>/ˈbrʌðə(r)/</t>
+  </si>
+  <si>
+    <t>bro-ther</t>
+  </si>
+  <si>
+    <t>/ˈsɪstə(r)/</t>
+  </si>
+  <si>
+    <t>sis-ter</t>
+  </si>
+  <si>
+    <t>/ˈʌŋkl/</t>
+  </si>
+  <si>
+    <t>un-cle</t>
+  </si>
+  <si>
+    <t>/ɑːnt/</t>
+  </si>
+  <si>
+    <t>--</t>
+  </si>
+  <si>
+    <t>/ˈkʌzn/</t>
+  </si>
+  <si>
+    <t>cous-in</t>
+  </si>
+  <si>
+    <t>/sʌn/</t>
+  </si>
+  <si>
+    <t>/ˈdɔːtə(r)/</t>
+  </si>
+  <si>
+    <t>daugh-ter</t>
+  </si>
+  <si>
+    <t>/ˈɡrænsʌn/</t>
+  </si>
+  <si>
+    <t>grand-son</t>
+  </si>
+  <si>
+    <t>/ˈɡrændɔːtə(r)/</t>
+  </si>
+  <si>
+    <t>grand-daugh-ter</t>
+  </si>
+  <si>
+    <t>/frendz/</t>
+  </si>
+  <si>
+    <t>/ˈklɑːsmeɪts/</t>
+  </si>
+  <si>
+    <t>class-mates</t>
+  </si>
+  <si>
+    <t>/ˈskuːlmeɪts/</t>
+  </si>
+  <si>
+    <t>school-mates</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -242,6 +362,23 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -251,12 +388,27 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDEE0E3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDEE0E3"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -265,7 +417,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -279,6 +431,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -595,13 +753,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{527ABE91-7216-BA4F-A91C-2F06E544A41C}">
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="32.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -611,8 +772,17 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="D1" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -622,8 +792,14 @@
       <c r="C2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="D2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
@@ -633,8 +809,14 @@
       <c r="C3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
+      <c r="D3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
@@ -644,8 +826,14 @@
       <c r="C4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:3">
+      <c r="D4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
@@ -655,8 +843,14 @@
       <c r="C5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:3">
+      <c r="D5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
@@ -666,8 +860,14 @@
       <c r="C6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:3">
+      <c r="D6" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
@@ -677,8 +877,14 @@
       <c r="C7">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:3">
+      <c r="D7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E7" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
@@ -688,8 +894,14 @@
       <c r="C8">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:3">
+      <c r="D8" t="s">
+        <v>67</v>
+      </c>
+      <c r="E8" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
@@ -699,8 +911,14 @@
       <c r="C9">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="1:3">
+      <c r="D9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="2" t="s">
         <v>11</v>
       </c>
@@ -710,8 +928,14 @@
       <c r="C10">
         <v>2</v>
       </c>
-    </row>
-    <row r="11" spans="1:3">
+      <c r="D10" t="s">
+        <v>71</v>
+      </c>
+      <c r="E10" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="2" t="s">
         <v>12</v>
       </c>
@@ -721,8 +945,14 @@
       <c r="C11">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="1:3">
+      <c r="D11" t="s">
+        <v>73</v>
+      </c>
+      <c r="E11" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="2" t="s">
         <v>13</v>
       </c>
@@ -732,8 +962,14 @@
       <c r="C12">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:3">
+      <c r="D12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E12" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="2" t="s">
         <v>14</v>
       </c>
@@ -743,8 +979,14 @@
       <c r="C13">
         <v>3</v>
       </c>
-    </row>
-    <row r="14" spans="1:3">
+      <c r="D13" t="s">
+        <v>77</v>
+      </c>
+      <c r="E13" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="2" t="s">
         <v>15</v>
       </c>
@@ -754,8 +996,14 @@
       <c r="C14">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:3">
+      <c r="D14" t="s">
+        <v>79</v>
+      </c>
+      <c r="E14" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="2" t="s">
         <v>16</v>
       </c>
@@ -765,8 +1013,14 @@
       <c r="C15">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:3">
+      <c r="D15" t="s">
+        <v>81</v>
+      </c>
+      <c r="E15" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" s="2" t="s">
         <v>17</v>
       </c>
@@ -776,8 +1030,14 @@
       <c r="C16">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:3">
+      <c r="D16" t="s">
+        <v>82</v>
+      </c>
+      <c r="E16" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" s="2" t="s">
         <v>18</v>
       </c>
@@ -787,8 +1047,14 @@
       <c r="C17">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
+      <c r="D17" t="s">
+        <v>84</v>
+      </c>
+      <c r="E17" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" s="2" t="s">
         <v>19</v>
       </c>
@@ -798,8 +1064,14 @@
       <c r="C18">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="1:3">
+      <c r="D18" t="s">
+        <v>86</v>
+      </c>
+      <c r="E18" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19" s="2" t="s">
         <v>20</v>
       </c>
@@ -809,8 +1081,14 @@
       <c r="C19">
         <v>4</v>
       </c>
-    </row>
-    <row r="20" spans="1:3">
+      <c r="D19" t="s">
+        <v>88</v>
+      </c>
+      <c r="E19" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20" s="2" t="s">
         <v>21</v>
       </c>
@@ -820,8 +1098,14 @@
       <c r="C20">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="1:3">
+      <c r="D20" t="s">
+        <v>89</v>
+      </c>
+      <c r="E20" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21" s="2" t="s">
         <v>22</v>
       </c>
@@ -831,36 +1115,42 @@
       <c r="C21">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="1:3">
+      <c r="D21" t="s">
+        <v>91</v>
+      </c>
+      <c r="E21" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22" s="2"/>
       <c r="B22" s="1"/>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:5">
       <c r="A23" s="2"/>
       <c r="B23" s="1"/>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:5">
       <c r="A24" s="2"/>
       <c r="B24" s="1"/>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:5">
       <c r="A25" s="2"/>
       <c r="B25" s="1"/>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:5">
       <c r="A26" s="2"/>
       <c r="B26" s="1"/>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:5">
       <c r="A27" s="2"/>
       <c r="B27" s="1"/>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:5">
       <c r="A28" s="2"/>
       <c r="B28" s="1"/>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:5">
       <c r="A29" s="2"/>
       <c r="B29" s="1"/>
     </row>

--- a/data/P1/P1T1_BQ1.xlsx
+++ b/data/P1/P1T1_BQ1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/單詞複習網素材/data/P1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/homes/ximonlam/Mac/單詞複習網素材/English/data/P1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D8F8F85-0B5B-2C48-A13B-0CE3BDB372CA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50740956-9425-1D4E-B54F-8FC5A9ADECA9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28460" yWindow="3780" windowWidth="30940" windowHeight="15020" xr2:uid="{90F29878-E095-0247-8CA8-B281629F062F}"/>
+    <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" xr2:uid="{90F29878-E095-0247-8CA8-B281629F062F}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="114">
   <si>
     <t>word</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -314,6 +314,70 @@
   </si>
   <si>
     <t>school-mates</t>
+  </si>
+  <si>
+    <t>English explanation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>all your people you live with, like mom, dad, grandparents</t>
+  </si>
+  <si>
+    <t>grandfather and grandmother together</t>
+  </si>
+  <si>
+    <t>dad’s dad or mom’s dad</t>
+  </si>
+  <si>
+    <t>dad’s mom or mom’s mom</t>
+  </si>
+  <si>
+    <t>father and mother together</t>
+  </si>
+  <si>
+    <t>your dad</t>
+  </si>
+  <si>
+    <t>your mom</t>
+  </si>
+  <si>
+    <t>your brothers and sisters</t>
+  </si>
+  <si>
+    <t>a boy who has the same mom and dad as you</t>
+  </si>
+  <si>
+    <t>a girl who has the same mom and dad as you</t>
+  </si>
+  <si>
+    <t>dad’s brother or mom’s brother</t>
+  </si>
+  <si>
+    <t>dad’s sister or mom’s sister</t>
+  </si>
+  <si>
+    <t>uncle’s or aunt’s child</t>
+  </si>
+  <si>
+    <t>a boy child of mom and dad</t>
+  </si>
+  <si>
+    <t>a girl child of mom and dad</t>
+  </si>
+  <si>
+    <t>son’s boy child</t>
+  </si>
+  <si>
+    <t>son’s girl child</t>
+  </si>
+  <si>
+    <t>people you like to play with</t>
+  </si>
+  <si>
+    <t>kids in your same class at school</t>
+  </si>
+  <si>
+    <t>kids in your same school</t>
   </si>
 </sst>
 </file>
@@ -417,7 +481,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -437,6 +501,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -760,6 +827,7 @@
     <col min="3" max="3" width="4.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="51.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -778,6 +846,9 @@
       <c r="E1" s="5" t="s">
         <v>54</v>
       </c>
+      <c r="F1" s="7" t="s">
+        <v>93</v>
+      </c>
       <c r="G1" s="6"/>
       <c r="H1" s="6"/>
       <c r="I1" s="6"/>
@@ -798,6 +869,9 @@
       <c r="E2" t="s">
         <v>56</v>
       </c>
+      <c r="F2" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="2" t="s">
@@ -815,6 +889,9 @@
       <c r="E3" t="s">
         <v>58</v>
       </c>
+      <c r="F3" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="2" t="s">
@@ -832,6 +909,9 @@
       <c r="E4" t="s">
         <v>60</v>
       </c>
+      <c r="F4" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="2" t="s">
@@ -849,6 +929,9 @@
       <c r="E5" t="s">
         <v>62</v>
       </c>
+      <c r="F5" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="2" t="s">
@@ -866,6 +949,9 @@
       <c r="E6" t="s">
         <v>64</v>
       </c>
+      <c r="F6" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="2" t="s">
@@ -883,6 +969,9 @@
       <c r="E7" t="s">
         <v>66</v>
       </c>
+      <c r="F7" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
@@ -900,6 +989,9 @@
       <c r="E8" t="s">
         <v>68</v>
       </c>
+      <c r="F8" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
@@ -917,6 +1009,9 @@
       <c r="E9" t="s">
         <v>70</v>
       </c>
+      <c r="F9" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="2" t="s">
@@ -934,6 +1029,9 @@
       <c r="E10" t="s">
         <v>72</v>
       </c>
+      <c r="F10" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="2" t="s">
@@ -951,6 +1049,9 @@
       <c r="E11" t="s">
         <v>74</v>
       </c>
+      <c r="F11" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="2" t="s">
@@ -968,6 +1069,9 @@
       <c r="E12" t="s">
         <v>76</v>
       </c>
+      <c r="F12" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="2" t="s">
@@ -985,6 +1089,9 @@
       <c r="E13" t="s">
         <v>78</v>
       </c>
+      <c r="F13" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="2" t="s">
@@ -1002,6 +1109,9 @@
       <c r="E14" t="s">
         <v>80</v>
       </c>
+      <c r="F14" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="2" t="s">
@@ -1019,6 +1129,9 @@
       <c r="E15" t="s">
         <v>78</v>
       </c>
+      <c r="F15" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="2" t="s">
@@ -1036,8 +1149,11 @@
       <c r="E16" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="17" spans="1:5">
+      <c r="F16" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" s="2" t="s">
         <v>18</v>
       </c>
@@ -1053,8 +1169,11 @@
       <c r="E17" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="18" spans="1:5">
+      <c r="F17" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18" s="2" t="s">
         <v>19</v>
       </c>
@@ -1070,8 +1189,11 @@
       <c r="E18" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="19" spans="1:5">
+      <c r="F18" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19" s="2" t="s">
         <v>20</v>
       </c>
@@ -1087,8 +1209,11 @@
       <c r="E19" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="20" spans="1:5">
+      <c r="F19" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20" s="2" t="s">
         <v>21</v>
       </c>
@@ -1104,8 +1229,11 @@
       <c r="E20" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="21" spans="1:5">
+      <c r="F20" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21" s="2" t="s">
         <v>22</v>
       </c>
@@ -1121,36 +1249,39 @@
       <c r="E21" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="22" spans="1:5">
+      <c r="F21" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22" s="2"/>
       <c r="B22" s="1"/>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:6">
       <c r="A23" s="2"/>
       <c r="B23" s="1"/>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:6">
       <c r="A24" s="2"/>
       <c r="B24" s="1"/>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:6">
       <c r="A25" s="2"/>
       <c r="B25" s="1"/>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:6">
       <c r="A26" s="2"/>
       <c r="B26" s="1"/>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:6">
       <c r="A27" s="2"/>
       <c r="B27" s="1"/>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:6">
       <c r="A28" s="2"/>
       <c r="B28" s="1"/>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:6">
       <c r="A29" s="2"/>
       <c r="B29" s="1"/>
     </row>
